--- a/output/第10期計画_図表集_白黒.xlsx
+++ b/output/第10期計画_図表集_白黒.xlsx
@@ -56315,7 +56315,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>出典：厚生労働省「保険者機能強化推進交付金・介護保険保険者努力支援交付金に係る評価指標（市町村分）」及び同「全国集計結果」令和6〜8年度（原本を令和8年9月2日受領）。令和8年度交付金は令和7年度（2025年度）に実施した取組を評価する。全国は1,745〜1,746市町村、北海道は179市町村の平均値。第10期基本指針の新別表 九「インセンティブ交付金における評価」に対応する。</t>
+          <t>出典：厚生労働省「保険者機能強化推進交付金・介護保険保険者努力支援交付金に係る評価指標（市町村分）」及び同「全国集計結果」令和6〜8年度（原本を令和8年9月2日受領）。令和8年度交付金は令和7年度（2025年度）に実施した取組を評価する。全国は1,741市町村、北海道は179市町村の平均値。第10期基本指針の新別表 九「インセンティブ交付金における評価」に対応する。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_図表集_白黒.xlsx
+++ b/output/第10期計画_図表集_白黒.xlsx
@@ -5677,7 +5677,7 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'23_上川中部圏域比較'!$A$22:$A$23</f>
+              <f>'23_上川中部圏域比較'!$A$21:$A$23</f>
             </numRef>
           </cat>
           <val>
@@ -5739,7 +5739,7 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'23_上川中部圏域比較'!$A$22:$A$23</f>
+              <f>'23_上川中部圏域比較'!$A$21:$A$23</f>
             </numRef>
           </cat>
           <val>
